--- a/src/output/results_consolidados_master.xlsx
+++ b/src/output/results_consolidados_master.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>config_num</t>
   </si>
@@ -40,7 +40,25 @@
     <t>exec</t>
   </si>
   <si>
-    <t>[30, 3, 2, 2, 2]</t>
+    <t>[29, 9, 29, 29, 31]</t>
+  </si>
+  <si>
+    <t>[17, 29, 17, 17, 23]</t>
+  </si>
+  <si>
+    <t>[17, 30, 29, 17, 17]</t>
+  </si>
+  <si>
+    <t>[0, 6, 12, 0, 7]</t>
+  </si>
+  <si>
+    <t>[12, 16, 23, 23, 12]</t>
+  </si>
+  <si>
+    <t>[21, 5, 21, 27, 14]</t>
+  </si>
+  <si>
+    <t>[21, 8, 21, 21, 16]</t>
   </si>
 </sst>
 </file>
@@ -398,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -438,19 +456,175 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>50.04433181828649</v>
+        <v>37.16487455259954</v>
       </c>
       <c r="E2">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>80.086938</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>49.13545004407987</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>87.08516</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>51.90016866052763</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>79.756109</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>50.98397950809326</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>85.85024199999999</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>51.1240248602771</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>79.515063</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>50.57577825945873</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>85.33426300000001</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="F2">
-        <v>82.29262900000001</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="D8">
+        <v>48.80058064405528</v>
+      </c>
+      <c r="E8">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>81.234189</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados_master.xlsx
+++ b/src/output/results_consolidados_master.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>config_num</t>
   </si>
@@ -40,25 +40,10 @@
     <t>exec</t>
   </si>
   <si>
-    <t>[29, 9, 29, 29, 31]</t>
-  </si>
-  <si>
-    <t>[17, 29, 17, 17, 23]</t>
-  </si>
-  <si>
-    <t>[17, 30, 29, 17, 17]</t>
-  </si>
-  <si>
-    <t>[0, 6, 12, 0, 7]</t>
-  </si>
-  <si>
-    <t>[12, 16, 23, 23, 12]</t>
-  </si>
-  <si>
-    <t>[21, 5, 21, 27, 14]</t>
-  </si>
-  <si>
-    <t>[21, 8, 21, 21, 16]</t>
+    <t>[26, 0, 19, 26, 12]</t>
+  </si>
+  <si>
+    <t>[8, 9, 22, 22, 8]</t>
   </si>
 </sst>
 </file>
@@ -416,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -456,13 +441,13 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>37.16487455259954</v>
+        <v>51.08384029266171</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>80.086938</v>
+        <v>112.716789</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -482,149 +467,19 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>49.13545004407987</v>
+        <v>50.62849554405395</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>87.08516</v>
+        <v>127.346984</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>51.90016866052763</v>
-      </c>
-      <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4">
-        <v>79.756109</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>50.98397950809326</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>85.85024199999999</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>51.1240248602771</v>
-      </c>
-      <c r="E6">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>79.515063</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7">
-        <v>50.57577825945873</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>85.33426300000001</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8">
-        <v>48.80058064405528</v>
-      </c>
-      <c r="E8">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>81.234189</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
